--- a/Results/Insulin Proportions/Insulin_Content_AO_Analysis.xlsx
+++ b/Results/Insulin Proportions/Insulin_Content_AO_Analysis.xlsx
@@ -1519,19 +1519,19 @@
         <v>111</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0886</v>
+        <v>0.0026</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0261</v>
+        <v>-0.0171</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1732</v>
+        <v>0.024</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0.6192</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.3807</v>
       </c>
     </row>
     <row r="7">
@@ -1539,19 +1539,19 @@
         <v>112</v>
       </c>
       <c r="B7" t="n">
-        <v>0.194</v>
+        <v>0.0553</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0571</v>
+        <v>-0.0107</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3492</v>
+        <v>0.1497</v>
       </c>
       <c r="E7" t="n">
-        <v>0.999</v>
+        <v>0.949</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="8">
@@ -1559,19 +1559,19 @@
         <v>113</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.037</v>
+        <v>0.0001</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0829</v>
+        <v>-0.019</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0064</v>
+        <v>0.0204</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0008</v>
+        <v>0.503</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9992</v>
+        <v>0.497</v>
       </c>
     </row>
     <row r="9">
@@ -1579,19 +1579,19 @@
         <v>114</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0493</v>
+        <v>0.0026</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0042</v>
+        <v>-0.0171</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1168</v>
+        <v>0.0254</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9905</v>
+        <v>0.6185</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0095</v>
+        <v>0.3815</v>
       </c>
     </row>
     <row r="10">
@@ -1599,19 +1599,19 @@
         <v>115</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0283</v>
+        <v>0.014</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1184</v>
+        <v>-0.0374</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0358</v>
+        <v>0.0747</v>
       </c>
       <c r="E10" t="n">
-        <v>0.184</v>
+        <v>0.7143</v>
       </c>
       <c r="F10" t="n">
-        <v>0.816</v>
+        <v>0.2858</v>
       </c>
     </row>
     <row r="11">
@@ -1619,19 +1619,19 @@
         <v>116</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1544</v>
+        <v>0.0555</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0072</v>
+        <v>-0.0132</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3278</v>
+        <v>0.1481</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9825</v>
+        <v>0.9502</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0175</v>
+        <v>0.0498</v>
       </c>
     </row>
     <row r="12">
@@ -1639,19 +1639,19 @@
         <v>117</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.0077</v>
+        <v>-0.0138</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.057</v>
+        <v>-0.0751</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0488</v>
+        <v>0.0393</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3548</v>
+        <v>0.2835</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6452</v>
+        <v>0.7165</v>
       </c>
     </row>
     <row r="13">
@@ -1659,19 +1659,19 @@
         <v>118</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0789</v>
+        <v>-0.0112</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0104</v>
+        <v>-0.071</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2041</v>
+        <v>0.0467</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9683</v>
+        <v>0.3362</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0318</v>
+        <v>0.6638</v>
       </c>
     </row>
     <row r="14">
@@ -1679,19 +1679,19 @@
         <v>119</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1868</v>
+        <v>0.0404</v>
       </c>
       <c r="C14" t="n">
-        <v>0.092</v>
+        <v>0.0077</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3102</v>
+        <v>0.0879</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="15">
@@ -1699,19 +1699,19 @@
         <v>120</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.1029</v>
+        <v>-0.0521</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.2794</v>
+        <v>-0.1435</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0663</v>
+        <v>0.0173</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1175</v>
+        <v>0.061</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8825</v>
+        <v>0.939</v>
       </c>
     </row>
     <row r="16">
@@ -1719,19 +1719,19 @@
         <v>121</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.0987</v>
+        <v>-0.0429</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.214</v>
+        <v>-0.123</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0061</v>
+        <v>0.0229</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0107</v>
+        <v>0.085</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9892</v>
+        <v>0.915</v>
       </c>
     </row>
     <row r="17">
@@ -1739,19 +1739,19 @@
         <v>122</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.0105</v>
+        <v>-0.0401</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1619</v>
+        <v>-0.1207</v>
       </c>
       <c r="D17" t="n">
-        <v>0.132</v>
+        <v>0.0277</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4387</v>
+        <v>0.1057</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5612</v>
+        <v>0.8942</v>
       </c>
     </row>
     <row r="18">
@@ -1759,19 +1759,19 @@
         <v>123</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.0604</v>
+        <v>-0.0428</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1876</v>
+        <v>-0.129</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0541</v>
+        <v>0.0187</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1405</v>
+        <v>0.0823</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8595</v>
+        <v>0.9178</v>
       </c>
     </row>
     <row r="19">
@@ -1779,19 +1779,19 @@
         <v>124</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.092</v>
+        <v>-0.0286</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.1681</v>
+        <v>-0.0697</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0339</v>
+        <v>-0.0009</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="20">
@@ -1799,19 +1799,19 @@
         <v>125</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0913</v>
+        <v>0.0118</v>
       </c>
       <c r="C20" t="n">
-        <v>0.026</v>
+        <v>-0.0228</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1689</v>
+        <v>0.0541</v>
       </c>
       <c r="E20" t="n">
-        <v>0.999</v>
+        <v>0.7702</v>
       </c>
       <c r="F20" t="n">
-        <v>0.001</v>
+        <v>0.2298</v>
       </c>
     </row>
   </sheetData>
@@ -1854,13 +1854,13 @@
         <v>49</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0319</v>
+        <v>0.0428</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0117</v>
+        <v>0.0192</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0582</v>
+        <v>0.0736</v>
       </c>
     </row>
     <row r="5">
@@ -1868,13 +1868,13 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1733</v>
+        <v>0.0656</v>
       </c>
       <c r="C5" t="n">
-        <v>0.093</v>
+        <v>0.0307</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2648</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="6">
@@ -1882,13 +1882,13 @@
         <v>51</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0994</v>
+        <v>0.0582</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0489</v>
+        <v>0.0261</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1645</v>
+        <v>0.0971</v>
       </c>
     </row>
     <row r="7">
@@ -1926,19 +1926,19 @@
         <v>58</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.1401</v>
+        <v>-0.0221</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.2164</v>
+        <v>-0.0495</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0798</v>
+        <v>-0.0025</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.0107</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.9892</v>
       </c>
     </row>
     <row r="11">
@@ -1946,19 +1946,19 @@
         <v>59</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0664</v>
+        <v>-0.0145</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.11</v>
+        <v>-0.0367</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0306</v>
+        <v>0.0031</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.0465</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.9535</v>
       </c>
     </row>
     <row r="12">
@@ -1966,19 +1966,19 @@
         <v>60</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0722</v>
+        <v>0.0076</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0305</v>
+        <v>-0.013</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1278</v>
+        <v>0.0309</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0.7768</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.2232</v>
       </c>
     </row>
   </sheetData>
@@ -2021,13 +2021,13 @@
         <v>63</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0695</v>
+        <v>0.0359</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0227</v>
+        <v>0.0126</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1391</v>
+        <v>0.0674</v>
       </c>
     </row>
     <row r="5">
@@ -2035,13 +2035,13 @@
         <v>64</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1287</v>
+        <v>0.073</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0526</v>
+        <v>0.0248</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2279</v>
+        <v>0.1407</v>
       </c>
     </row>
     <row r="6">
@@ -2079,19 +2079,19 @@
         <v>66</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0572</v>
+        <v>-0.0364</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1721</v>
+        <v>-0.1114</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0494</v>
+        <v>0.0222</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1375</v>
+        <v>0.103</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8625</v>
+        <v>0.897</v>
       </c>
     </row>
   </sheetData>
@@ -2140,13 +2140,13 @@
         <v>63</v>
       </c>
       <c r="C4" t="n">
-        <v>0.026</v>
+        <v>0.0347</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0063</v>
+        <v>0.0115</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0628</v>
+        <v>0.0679</v>
       </c>
     </row>
     <row r="5">
@@ -2157,13 +2157,13 @@
         <v>64</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0348</v>
+        <v>0.0485</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0082</v>
+        <v>0.0144</v>
       </c>
       <c r="E5" t="n">
-        <v>0.078</v>
+        <v>0.1035</v>
       </c>
     </row>
     <row r="6">
@@ -2174,13 +2174,13 @@
         <v>63</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1168</v>
+        <v>0.0373</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0346</v>
+        <v>0.0117</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2242</v>
+        <v>0.0736</v>
       </c>
     </row>
     <row r="7">
@@ -2191,13 +2191,13 @@
         <v>64</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2231</v>
+        <v>0.0911</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0969</v>
+        <v>0.0323</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3748</v>
+        <v>0.1763</v>
       </c>
     </row>
     <row r="8">
@@ -2208,13 +2208,13 @@
         <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0647</v>
+        <v>0.0344</v>
       </c>
       <c r="D8" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1327</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="9">
@@ -2225,13 +2225,13 @@
         <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1273</v>
+        <v>0.0783</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0477</v>
+        <v>0.0249</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2396</v>
+        <v>0.1529</v>
       </c>
     </row>
     <row r="10">
@@ -2275,19 +2275,19 @@
         <v>49</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0077</v>
+        <v>-0.0138</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.057</v>
+        <v>-0.0751</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0488</v>
+        <v>0.0393</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3548</v>
+        <v>0.2835</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6452</v>
+        <v>0.7165</v>
       </c>
     </row>
     <row r="14">
@@ -2298,19 +2298,19 @@
         <v>50</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1029</v>
+        <v>-0.0521</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2794</v>
+        <v>-0.1435</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0663</v>
+        <v>0.0173</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1175</v>
+        <v>0.061</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8825</v>
+        <v>0.939</v>
       </c>
     </row>
     <row r="15">
@@ -2321,19 +2321,19 @@
         <v>51</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0604</v>
+        <v>-0.0428</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1876</v>
+        <v>-0.129</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0541</v>
+        <v>0.0187</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1405</v>
+        <v>0.0823</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8595</v>
+        <v>0.9178</v>
       </c>
     </row>
     <row r="16">
@@ -2377,19 +2377,19 @@
         <v>63</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0886</v>
+        <v>-0.0026</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1732</v>
+        <v>-0.024</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0261</v>
+        <v>0.0171</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.3807</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0.6192</v>
       </c>
     </row>
     <row r="20">
@@ -2400,19 +2400,19 @@
         <v>63</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.037</v>
+        <v>0.0001</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0829</v>
+        <v>-0.019</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0064</v>
+        <v>0.0204</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0008</v>
+        <v>0.503</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9992</v>
+        <v>0.497</v>
       </c>
     </row>
     <row r="21">
@@ -2423,19 +2423,19 @@
         <v>63</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0493</v>
+        <v>0.0026</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0042</v>
+        <v>-0.0171</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1168</v>
+        <v>0.0254</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9905</v>
+        <v>0.6185</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0095</v>
+        <v>0.3815</v>
       </c>
     </row>
     <row r="22">
@@ -2446,19 +2446,19 @@
         <v>64</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1868</v>
+        <v>-0.0404</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3102</v>
+        <v>-0.0879</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.092</v>
+        <v>-0.0077</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.0027</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
     </row>
     <row r="23">
@@ -2469,19 +2469,19 @@
         <v>64</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.092</v>
+        <v>-0.0286</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1681</v>
+        <v>-0.0697</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0339</v>
+        <v>-0.0009</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="24">
@@ -2492,19 +2492,19 @@
         <v>64</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0913</v>
+        <v>0.0118</v>
       </c>
       <c r="D24" t="n">
-        <v>0.026</v>
+        <v>-0.0228</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1689</v>
+        <v>0.0541</v>
       </c>
       <c r="F24" t="n">
-        <v>0.999</v>
+        <v>0.7702</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001</v>
+        <v>0.2298</v>
       </c>
     </row>
   </sheetData>
@@ -2558,13 +2558,13 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.0289</v>
+        <v>-0.0174</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0477</v>
+        <v>-0.0318</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0122</v>
+        <v>-0.0069</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2608,19 +2608,19 @@
         <v>49</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0077</v>
+        <v>-0.012</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0179</v>
+        <v>-0.0242</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0004</v>
+        <v>-0.0041</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0015</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9985</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -2628,13 +2628,13 @@
         <v>50</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0515</v>
+        <v>-0.0213</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0783</v>
+        <v>-0.0386</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.024</v>
+        <v>-0.0086</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>51</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0274</v>
+        <v>-0.0186</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0493</v>
+        <v>-0.0341</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0092</v>
+        <v>-0.0072</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -2698,19 +2698,19 @@
         <v>58</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0433</v>
+        <v>0.009</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0214</v>
+        <v>0.0021</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0638</v>
+        <v>0.0178</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.9978</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="16">
@@ -2718,19 +2718,19 @@
         <v>59</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0192</v>
+        <v>0.0061</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0066</v>
+        <v>0.0004</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0338</v>
+        <v>0.0136</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0.9862</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.0138</v>
       </c>
     </row>
     <row r="17">
@@ -2738,19 +2738,19 @@
         <v>60</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.0232</v>
+        <v>-0.0028</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0393</v>
+        <v>-0.0095</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0085</v>
+        <v>0.0039</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0008</v>
+        <v>0.183</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9992</v>
+        <v>0.817</v>
       </c>
     </row>
     <row r="18">
@@ -2788,19 +2788,19 @@
         <v>63</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.0159</v>
+        <v>-0.0079</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0356</v>
+        <v>-0.0173</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0019</v>
+        <v>-0.0017</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0005</v>
+        <v>0.0015</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9995</v>
+        <v>0.9985</v>
       </c>
     </row>
     <row r="22">
@@ -2808,13 +2808,13 @@
         <v>64</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.0405</v>
+        <v>-0.0259</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0728</v>
+        <v>-0.0523</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0128</v>
+        <v>-0.0063</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -2858,19 +2858,19 @@
         <v>66</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0238</v>
+        <v>0.0177</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0077</v>
+        <v>-0.0059</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0615</v>
+        <v>0.0442</v>
       </c>
       <c r="E26" t="n">
-        <v>0.924</v>
+        <v>0.9525</v>
       </c>
       <c r="F26" t="n">
-        <v>0.076</v>
+        <v>0.0475</v>
       </c>
     </row>
   </sheetData>
@@ -2924,19 +2924,19 @@
         <v>24</v>
       </c>
       <c r="B5" t="n">
-        <v>0.001</v>
+        <v>-0.0004</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0091</v>
+        <v>-0.0078</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0103</v>
+        <v>0.0053</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5885</v>
+        <v>0.453</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4115</v>
+        <v>0.547</v>
       </c>
     </row>
     <row r="6">
@@ -2974,19 +2974,19 @@
         <v>49</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0017</v>
+        <v>-0.0018</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0075</v>
+        <v>-0.0087</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003</v>
+        <v>0.0031</v>
       </c>
       <c r="E9" t="n">
-        <v>0.193</v>
+        <v>0.2245</v>
       </c>
       <c r="F9" t="n">
-        <v>0.807</v>
+        <v>0.7755</v>
       </c>
     </row>
     <row r="10">
@@ -2994,19 +2994,19 @@
         <v>50</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0053</v>
+        <v>0.0012</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0089</v>
+        <v>-0.0073</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0195</v>
+        <v>0.0075</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7805</v>
+        <v>0.6312</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2195</v>
+        <v>0.3688</v>
       </c>
     </row>
     <row r="11">
@@ -3014,19 +3014,19 @@
         <v>51</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0005</v>
+        <v>-0.0004</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0115</v>
+        <v>-0.0084</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0103</v>
+        <v>0.0059</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4552</v>
+        <v>0.444</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5448</v>
+        <v>0.556</v>
       </c>
     </row>
     <row r="12">
@@ -3064,19 +3064,19 @@
         <v>58</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0072</v>
+        <v>-0.003</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0181</v>
+        <v>-0.0069</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0028</v>
+        <v>0.0009</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0782</v>
+        <v>0.0508</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9218</v>
+        <v>0.9492</v>
       </c>
     </row>
     <row r="16">
@@ -3084,19 +3084,19 @@
         <v>59</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.0013</v>
+        <v>-0.0014</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0086</v>
+        <v>-0.0048</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0053</v>
+        <v>0.0021</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3398</v>
+        <v>0.2052</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6602</v>
+        <v>0.7948</v>
       </c>
     </row>
     <row r="17">
@@ -3104,19 +3104,19 @@
         <v>60</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0059</v>
+        <v>0.0016</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0008</v>
+        <v>-0.0016</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0125</v>
+        <v>0.005</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9708</v>
+        <v>0.857</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0293</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="18">
@@ -3154,19 +3154,19 @@
         <v>63</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0077</v>
+        <v>0.004</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0013</v>
+        <v>0.0004</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0178</v>
+        <v>0.0095</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9982</v>
+        <v>0.9962</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0018</v>
+        <v>0.0037</v>
       </c>
     </row>
     <row r="22">
@@ -3174,19 +3174,19 @@
         <v>64</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.006</v>
+        <v>-0.0048</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0232</v>
+        <v>-0.0182</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0082</v>
+        <v>0.0047</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1955</v>
+        <v>0.1398</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8045</v>
+        <v>0.8602</v>
       </c>
     </row>
     <row r="23">
@@ -3224,19 +3224,19 @@
         <v>66</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0146</v>
+        <v>0.0094</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0012</v>
+        <v>-0.0006</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0327</v>
+        <v>0.0242</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9738</v>
+        <v>0.9785</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0262</v>
+        <v>0.0215</v>
       </c>
     </row>
   </sheetData>
@@ -3290,13 +3290,13 @@
         <v>25</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0131</v>
+        <v>0.0104</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0068</v>
+        <v>0.0053</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0203</v>
+        <v>0.0158</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3343,10 +3343,10 @@
         <v>0.0185</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0084</v>
+        <v>0.0096</v>
       </c>
       <c r="D9" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -3360,19 +3360,19 @@
         <v>50</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0018</v>
+        <v>0.0035</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0047</v>
+        <v>-0.0001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0082</v>
+        <v>0.0081</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7155</v>
+        <v>0.975</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2845</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="11">
@@ -3380,13 +3380,13 @@
         <v>51</v>
       </c>
       <c r="B11" t="n">
-        <v>0.019</v>
+        <v>0.0091</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0108</v>
+        <v>0.0048</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0273</v>
+        <v>0.0146</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -3430,13 +3430,13 @@
         <v>58</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0169</v>
+        <v>0.015</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0057</v>
+        <v>0.007</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0302</v>
+        <v>0.025</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -3450,19 +3450,19 @@
         <v>59</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.0003</v>
+        <v>0.0094</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0064</v>
+        <v>0.0031</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0072</v>
+        <v>0.017</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4622</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5378</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3470,19 +3470,19 @@
         <v>60</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.0171</v>
+        <v>-0.0054</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0271</v>
+        <v>-0.0115</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0072</v>
+        <v>-0.0005</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.0088</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0.9912</v>
       </c>
     </row>
     <row r="18">
@@ -3520,13 +3520,13 @@
         <v>63</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0112</v>
+        <v>0.0086</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0041</v>
+        <v>0.0034</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0221</v>
+        <v>0.015</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -3540,13 +3540,13 @@
         <v>64</v>
       </c>
       <c r="B22" t="n">
-        <v>0.0144</v>
+        <v>0.0119</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0059</v>
+        <v>0.0047</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0257</v>
+        <v>0.0212</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -3590,19 +3590,19 @@
         <v>66</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.0029</v>
+        <v>-0.0033</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0166</v>
+        <v>-0.0141</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0111</v>
+        <v>0.0066</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3278</v>
+        <v>0.2517</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6722</v>
+        <v>0.7482</v>
       </c>
     </row>
   </sheetData>
@@ -3677,19 +3677,19 @@
         <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0082</v>
+        <v>-0.0128</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0202</v>
+        <v>-0.0264</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0011</v>
+        <v>-0.0036</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9995</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -3700,13 +3700,13 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0494</v>
+        <v>-0.0206</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0772</v>
+        <v>-0.0383</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0243</v>
+        <v>-0.0067</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -3723,13 +3723,13 @@
         <v>96</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0274</v>
+        <v>-0.0187</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.049</v>
+        <v>-0.0352</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0085</v>
+        <v>-0.0058</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -3746,19 +3746,19 @@
         <v>97</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0071</v>
+        <v>-0.0114</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0171</v>
+        <v>-0.0216</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0006</v>
+        <v>-0.0037</v>
       </c>
       <c r="F11" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.997</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -3769,13 +3769,13 @@
         <v>97</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.0535</v>
+        <v>-0.0222</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.083</v>
+        <v>-0.0382</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0264</v>
+        <v>-0.0097</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -3792,13 +3792,13 @@
         <v>97</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0275</v>
+        <v>-0.0185</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0495</v>
+        <v>-0.0321</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0091</v>
+        <v>-0.0072</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -3848,19 +3848,19 @@
         <v>99</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0011</v>
+        <v>0.0013</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0015</v>
+        <v>-0.0014</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0052</v>
+        <v>0.0058</v>
       </c>
       <c r="F17" t="n">
-        <v>0.832</v>
+        <v>0.8238</v>
       </c>
       <c r="G17" t="n">
-        <v>0.168</v>
+        <v>0.1762</v>
       </c>
     </row>
     <row r="18">
@@ -3871,19 +3871,19 @@
         <v>99</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0041</v>
+        <v>-0.0013</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0112</v>
+        <v>-0.005</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0021</v>
+        <v>0.003</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0978</v>
+        <v>0.26</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9022</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="19">
@@ -3894,19 +3894,19 @@
         <v>99</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0051</v>
+        <v>-0.0032</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0057</v>
+        <v>0.0048</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5128</v>
+        <v>0.5545</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4872</v>
+        <v>0.4455</v>
       </c>
     </row>
   </sheetData>
@@ -3981,19 +3981,19 @@
         <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.004</v>
+        <v>-0.0074</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0107</v>
+        <v>-0.0159</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001</v>
+        <v>-0.0018</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006</v>
+        <v>0.0003</v>
       </c>
       <c r="G8" t="n">
-        <v>0.994</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="9">
@@ -4004,13 +4004,13 @@
         <v>105</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0541</v>
+        <v>-0.0219</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0838</v>
+        <v>-0.039</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0273</v>
+        <v>-0.0085</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -4027,13 +4027,13 @@
         <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0229</v>
+        <v>-0.0158</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0432</v>
+        <v>-0.03</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0066</v>
+        <v>-0.0055</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -4050,19 +4050,19 @@
         <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0137</v>
+        <v>-0.0188</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0292</v>
+        <v>-0.0346</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0026</v>
+        <v>-0.0075</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -4073,13 +4073,13 @@
         <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.0486</v>
+        <v>-0.0206</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0758</v>
+        <v>-0.0377</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0231</v>
+        <v>-0.0079</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -4096,13 +4096,13 @@
         <v>106</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0323</v>
+        <v>-0.0217</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0547</v>
+        <v>-0.0384</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0113</v>
+        <v>-0.0089</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -4152,19 +4152,19 @@
         <v>108</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0097</v>
+        <v>-0.0114</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0187</v>
+        <v>-0.0184</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0028</v>
+        <v>-0.0052</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -4175,19 +4175,19 @@
         <v>108</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0054</v>
+        <v>0.0013</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0011</v>
+        <v>-0.0007</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0102</v>
+        <v>0.0035</v>
       </c>
       <c r="F18" t="n">
-        <v>0.994</v>
+        <v>0.912</v>
       </c>
       <c r="G18" t="n">
-        <v>0.006</v>
+        <v>0.088</v>
       </c>
     </row>
     <row r="19">
@@ -4198,13 +4198,13 @@
         <v>108</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0091</v>
+        <v>-0.0058</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0139</v>
+        <v>-0.0086</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0049</v>
+        <v>-0.0028</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
